--- a/data/trans_dic/KIDM_A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_A_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 12,03</t>
+          <t>1,42; 11,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,22</t>
+          <t>0,0; 8,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,67</t>
+          <t>0,0; 17,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>0,0; 7,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,73</t>
+          <t>0,0; 10,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,69</t>
+          <t>0,0; 30,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,07</t>
+          <t>0,73; 6,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,47</t>
+          <t>0,66; 5,92</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 9,27</t>
+          <t>1,08; 9,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,19</t>
+          <t>0,0; 18,33</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,11</t>
+          <t>0,64; 3,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,85</t>
+          <t>1,39; 5,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,78</t>
+          <t>0,51; 3,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 4,2</t>
+          <t>0,22; 3,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,15</t>
+          <t>0,67; 3,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 8,03</t>
+          <t>3,01; 7,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,31</t>
+          <t>0,08; 3,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,23</t>
+          <t>1,01; 3,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,14</t>
+          <t>2,67; 6,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,29</t>
+          <t>0,42; 2,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,61</t>
+          <t>0,43; 2,36</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,87</t>
+          <t>0,0; 6,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 10,6</t>
+          <t>1,28; 10,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 4,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>0,0; 7,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,85</t>
+          <t>0,0; 10,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,71</t>
+          <t>0,95; 10,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,04</t>
+          <t>0,65; 6,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,63</t>
+          <t>0,68; 5,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,85</t>
+          <t>0,92; 5,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,9</t>
+          <t>0,99; 4,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,21</t>
+          <t>1,68; 5,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,95</t>
+          <t>0,7; 2,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,17</t>
+          <t>0,32; 3,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,47</t>
+          <t>0,89; 3,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,77</t>
+          <t>2,16; 5,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,47</t>
+          <t>0,75; 3,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,0</t>
+          <t>0,37; 3,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,25</t>
+          <t>1,23; 3,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,84</t>
+          <t>2,28; 4,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,62</t>
+          <t>0,99; 2,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,4</t>
+          <t>0,56; 2,45</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1518</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2231</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>632; 5344</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4056</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5093</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3487</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3944</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5114</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>633; 5629</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>618; 5509</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>709; 6087</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5345</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3387</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5695</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2916</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4174</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10759</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1788</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1801</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7561</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>16453</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4703</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3834</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1177; 7314</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2602; 10772</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1163; 7080</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>353; 5915</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1407; 8324</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6454; 16935</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6387</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>168; 6215</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4003; 12940</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>10695; 24824</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1848; 9572</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1570; 8585</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2318</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2186</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2318</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3613</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>742; 6265</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3135</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2715</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4964</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>698; 7618</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>658; 6336</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>758; 6357</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1287; 8098</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3030</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6085</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9344</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5051</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2650</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5634</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11382</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5546</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3568</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11719</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>20726</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10597</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2795; 11970</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4907; 15396</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2254; 9348</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>684; 6553</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2687; 10342</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>6736; 17923</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2453; 11722</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1015; 8430</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>7173; 18806</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>13781; 28689</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>6434; 16695</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2712; 11845</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/KIDM_A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_A_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 11,97</t>
+          <t>1,43; 11,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,47</t>
+          <t>0,0; 8,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,43</t>
+          <t>0,0; 15,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,72</t>
+          <t>0,0; 7,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,76</t>
+          <t>0,0; 10,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,53</t>
+          <t>0,0; 32,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,45</t>
+          <t>0,72; 6,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,92</t>
+          <t>0,67; 5,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,24</t>
+          <t>1,08; 10,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,33</t>
+          <t>0,0; 18,93</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,95</t>
+          <t>0,68; 4,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,78</t>
+          <t>1,35; 5,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,1</t>
+          <t>0,46; 2,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,69</t>
+          <t>0,31; 3,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,94</t>
+          <t>0,92; 3,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,91</t>
+          <t>3,04; 7,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,05</t>
+          <t>0,09; 2,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,27</t>
+          <t>1,03; 3,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,2</t>
+          <t>2,7; 5,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,15</t>
+          <t>0,42; 2,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,36</t>
+          <t>0,35; 2,35</t>
         </is>
       </c>
     </row>
@@ -997,27 +997,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,77</t>
+          <t>0,0; 6,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 10,84</t>
+          <t>1,31; 10,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,73</t>
+          <t>0,0; 4,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,01</t>
+          <t>0,0; 8,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,23</t>
+          <t>0,0; 9,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 10,34</t>
+          <t>0,93; 9,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,22</t>
+          <t>0,65; 6,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,74</t>
+          <t>0,68; 5,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,79</t>
+          <t>0,94; 5,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,23</t>
+          <t>0,99; 3,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,27</t>
+          <t>1,87; 5,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,88</t>
+          <t>0,67; 2,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,1</t>
+          <t>0,35; 3,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,42</t>
+          <t>0,83; 3,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,74</t>
+          <t>2,28; 5,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,6</t>
+          <t>0,75; 3,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,09</t>
+          <t>0,38; 3,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,21</t>
+          <t>1,16; 3,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,75</t>
+          <t>2,22; 4,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,57</t>
+          <t>0,91; 2,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,45</t>
+          <t>0,55; 2,58</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,17 +1504,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>632; 5344</t>
+          <t>639; 5349</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4056</t>
+          <t>0; 4270</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5093</t>
+          <t>0; 4671</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1529,37 +1529,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3487</t>
+          <t>0; 3244</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3944</t>
+          <t>0; 3969</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5114</t>
+          <t>0; 5495</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>633; 5629</t>
+          <t>630; 5262</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>618; 5509</t>
+          <t>627; 5232</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>709; 6087</t>
+          <t>713; 6735</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5345</t>
+          <t>0; 5520</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1177; 7314</t>
+          <t>1255; 7763</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2602; 10772</t>
+          <t>2524; 10316</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1163; 7080</t>
+          <t>1058; 6394</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>353; 5915</t>
+          <t>497; 6260</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1407; 8324</t>
+          <t>1942; 8373</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6454; 16935</t>
+          <t>6505; 16628</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6387</t>
+          <t>0; 6301</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>168; 6215</t>
+          <t>184; 5347</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4003; 12940</t>
+          <t>4064; 13368</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10695; 24824</t>
+          <t>10814; 23417</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1848; 9572</t>
+          <t>1881; 9365</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1570; 8585</t>
+          <t>1282; 8564</t>
         </is>
       </c>
     </row>
@@ -1920,27 +1920,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3613</t>
+          <t>0; 3620</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>742; 6265</t>
+          <t>759; 6309</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3135</t>
+          <t>0; 3120</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2715</t>
+          <t>0; 3215</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4964</t>
+          <t>0; 4642</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>698; 7618</t>
+          <t>685; 6982</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>658; 6336</t>
+          <t>662; 6626</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>758; 6357</t>
+          <t>753; 6158</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1287; 8098</t>
+          <t>1316; 8041</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3030</t>
+          <t>0; 2598</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2795; 11970</t>
+          <t>2791; 11054</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4907; 15396</t>
+          <t>5479; 16503</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2254; 9348</t>
+          <t>2156; 9219</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>684; 6553</t>
+          <t>743; 7180</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2687; 10342</t>
+          <t>2507; 11529</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6736; 17923</t>
+          <t>7120; 17336</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2453; 11722</t>
+          <t>2438; 11252</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1015; 8430</t>
+          <t>1033; 9551</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7173; 18806</t>
+          <t>6774; 17910</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13781; 28689</t>
+          <t>13409; 28347</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6434; 16695</t>
+          <t>5896; 16314</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2712; 11845</t>
+          <t>2673; 12489</t>
         </is>
       </c>
     </row>
